--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_Auto_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_Auto_Fiets.xlsx
@@ -388,10 +388,10 @@
         <v>891</v>
       </c>
       <c r="C2">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="D2">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="E2">
         <v>1641</v>
@@ -405,10 +405,10 @@
         <v>919</v>
       </c>
       <c r="C3">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="D3">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="E3">
         <v>1650</v>
@@ -422,10 +422,10 @@
         <v>848</v>
       </c>
       <c r="C4">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="D4">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="E4">
         <v>1629</v>
@@ -479,7 +479,7 @@
         <v>1552</v>
       </c>
       <c r="E7">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -490,13 +490,13 @@
         <v>858</v>
       </c>
       <c r="C8">
-        <v>1251</v>
+        <v>1262</v>
       </c>
       <c r="D8">
-        <v>1492</v>
+        <v>1502</v>
       </c>
       <c r="E8">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -507,7 +507,7 @@
         <v>968</v>
       </c>
       <c r="C9">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="D9">
         <v>1546</v>
